--- a/data/review/review_needed.xlsx
+++ b/data/review/review_needed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T531"/>
+  <dimension ref="A1:T532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30550,6 +30550,64 @@
       <c r="S531" t="inlineStr"/>
       <c r="T531" t="inlineStr"/>
     </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>node/8350491453</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Dizzy Eagle</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>bar_with_food</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Multiple menu sources confirm the venue offers food, but no specific cuisine, food specialties, or regional/country origins are mentioned. The venue is tagged as a bar, and evidence does not indicate substantial savory meals from a defined cuisine.</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>official_menu (https://restaurantguru.com/DizzyEagle-Chisinau/menu); delivery_platform (https://glovoapp.com/md/en/chisinau/dizzy-eagle/); osm</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr"/>
+      <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="n">
+        <v>47.043144</v>
+      </c>
+      <c r="R532" t="n">
+        <v>28.772182</v>
+      </c>
+      <c r="S532" t="inlineStr"/>
+      <c r="T532" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
